--- a/history_prices/MAY/prices_01052026.xlsx
+++ b/history_prices/MAY/prices_01052026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\history_prices\MAY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95B29BA-F782-4678-8EE9-CB29A644CECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDB6C2D-6383-4E3A-B161-699E05FABE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="444">
   <si>
     <t>ID</t>
   </si>
@@ -1343,6 +1343,15 @@
   </si>
   <si>
     <t>0389</t>
+  </si>
+  <si>
+    <t>ОБЩИНА АКСАКОВО 1</t>
+  </si>
+  <si>
+    <t>ОБЩИНА АКСАКОВО 2</t>
+  </si>
+  <si>
+    <t>000093385</t>
   </si>
 </sst>
 </file>
@@ -1350,9 +1359,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.00_-"/>
-    <numFmt numFmtId="167" formatCode="&quot;€&quot;#,##0.000_-"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="&quot;€&quot;#,##0.00_-"/>
+    <numFmt numFmtId="166" formatCode="&quot;€&quot;#,##0.000_-"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -1383,11 +1392,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1690,7 +1700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N251"/>
+  <dimension ref="A1:N261"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.28515625" customWidth="1"/>
@@ -9436,7 +9446,298 @@
         <v>437</v>
       </c>
     </row>
+    <row r="252" spans="1:14" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>377</v>
+      </c>
+      <c r="B252" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C252" t="s">
+        <v>441</v>
+      </c>
+      <c r="D252" t="s">
+        <v>16</v>
+      </c>
+      <c r="E252" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F252" s="3">
+        <v>1.6359999999999999</v>
+      </c>
+      <c r="G252" s="3">
+        <v>0</v>
+      </c>
+      <c r="H252" s="2">
+        <v>1.6359999999999999</v>
+      </c>
+      <c r="N252" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>380</v>
+      </c>
+      <c r="B253" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C253" t="s">
+        <v>441</v>
+      </c>
+      <c r="D253" t="s">
+        <v>70</v>
+      </c>
+      <c r="E253" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F253" s="3">
+        <v>1.776</v>
+      </c>
+      <c r="G253" s="3">
+        <v>0</v>
+      </c>
+      <c r="H253" s="2">
+        <v>1.776</v>
+      </c>
+      <c r="N253" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>381</v>
+      </c>
+      <c r="B254" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C254" t="s">
+        <v>441</v>
+      </c>
+      <c r="D254" t="s">
+        <v>21</v>
+      </c>
+      <c r="E254" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F254" s="3">
+        <v>1.401</v>
+      </c>
+      <c r="G254" s="3">
+        <v>0</v>
+      </c>
+      <c r="H254" s="2">
+        <v>1.401</v>
+      </c>
+      <c r="N254" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>382</v>
+      </c>
+      <c r="B255" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C255" t="s">
+        <v>441</v>
+      </c>
+      <c r="D255" t="s">
+        <v>73</v>
+      </c>
+      <c r="E255" s="2">
+        <v>0</v>
+      </c>
+      <c r="F255" s="3">
+        <v>1.6559999999999999</v>
+      </c>
+      <c r="G255" s="3">
+        <v>0</v>
+      </c>
+      <c r="H255" s="2">
+        <v>1.6559999999999999</v>
+      </c>
+      <c r="N255" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="256" spans="1:14" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>383</v>
+      </c>
+      <c r="B256" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C256" t="s">
+        <v>441</v>
+      </c>
+      <c r="D256" t="s">
+        <v>229</v>
+      </c>
+      <c r="E256" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="F256" s="3">
+        <v>1</v>
+      </c>
+      <c r="G256" s="3">
+        <v>0</v>
+      </c>
+      <c r="H256" s="2">
+        <v>1</v>
+      </c>
+      <c r="N256" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>377</v>
+      </c>
+      <c r="B257" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C257" t="s">
+        <v>442</v>
+      </c>
+      <c r="D257" t="s">
+        <v>16</v>
+      </c>
+      <c r="E257" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F257" s="3">
+        <v>1.6359999999999999</v>
+      </c>
+      <c r="G257" s="3">
+        <v>0</v>
+      </c>
+      <c r="H257" s="2">
+        <v>1.6359999999999999</v>
+      </c>
+      <c r="N257" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>380</v>
+      </c>
+      <c r="B258" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C258" t="s">
+        <v>442</v>
+      </c>
+      <c r="D258" t="s">
+        <v>70</v>
+      </c>
+      <c r="E258" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F258" s="3">
+        <v>1.776</v>
+      </c>
+      <c r="G258" s="3">
+        <v>0</v>
+      </c>
+      <c r="H258" s="2">
+        <v>1.776</v>
+      </c>
+      <c r="N258" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>381</v>
+      </c>
+      <c r="B259" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C259" t="s">
+        <v>442</v>
+      </c>
+      <c r="D259" t="s">
+        <v>21</v>
+      </c>
+      <c r="E259" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F259" s="3">
+        <v>1.401</v>
+      </c>
+      <c r="G259" s="3">
+        <v>0</v>
+      </c>
+      <c r="H259" s="2">
+        <v>1.401</v>
+      </c>
+      <c r="N259" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>382</v>
+      </c>
+      <c r="B260" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C260" t="s">
+        <v>442</v>
+      </c>
+      <c r="D260" t="s">
+        <v>73</v>
+      </c>
+      <c r="E260" s="2">
+        <v>0</v>
+      </c>
+      <c r="F260" s="3">
+        <v>1.6559999999999999</v>
+      </c>
+      <c r="G260" s="3">
+        <v>0</v>
+      </c>
+      <c r="H260" s="2">
+        <v>1.6559999999999999</v>
+      </c>
+      <c r="N260" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>383</v>
+      </c>
+      <c r="B261" s="1">
+        <v>46143</v>
+      </c>
+      <c r="C261" t="s">
+        <v>442</v>
+      </c>
+      <c r="D261" t="s">
+        <v>229</v>
+      </c>
+      <c r="E261" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="F261" s="3">
+        <v>1</v>
+      </c>
+      <c r="G261" s="3">
+        <v>0</v>
+      </c>
+      <c r="H261" s="2">
+        <v>1</v>
+      </c>
+      <c r="N261" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>